--- a/artfynd/A 31161-2025 artfynd.xlsx
+++ b/artfynd/A 31161-2025 artfynd.xlsx
@@ -777,7 +777,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -896,7 +896,7 @@
         <v>127154208</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1096,39 +1096,39 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127154682</v>
+        <v>127154206</v>
       </c>
       <c r="B6" t="n">
-        <v>5176</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1136,12 +1136,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1151,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466105</v>
+        <v>466190</v>
       </c>
       <c r="R6" t="n">
-        <v>6809170</v>
+        <v>6809189</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1194,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1207,44 +1205,54 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127154246</v>
+        <v>127154682</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>5176</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1252,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466177</v>
+        <v>466105</v>
       </c>
       <c r="R7" t="n">
-        <v>6809177</v>
+        <v>6809170</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,17 +1316,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127154206</v>
+        <v>127154246</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1326,35 +1334,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1362,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466190</v>
+        <v>466177</v>
       </c>
       <c r="R8" t="n">
-        <v>6809189</v>
+        <v>6809177</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,6 +1405,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1427,7 +1427,7 @@
         <v>127154796</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 31161-2025 artfynd.xlsx
+++ b/artfynd/A 31161-2025 artfynd.xlsx
@@ -777,7 +777,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -896,7 +896,7 @@
         <v>127154208</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1096,39 +1096,39 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127154206</v>
+        <v>127154682</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>5176</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1136,11 +1136,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1150,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466190</v>
+        <v>466105</v>
       </c>
       <c r="R6" t="n">
-        <v>6809189</v>
+        <v>6809170</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,6 +1195,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1205,54 +1207,44 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127154682</v>
+        <v>127154246</v>
       </c>
       <c r="B7" t="n">
-        <v>5176</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1260,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466105</v>
+        <v>466177</v>
       </c>
       <c r="R7" t="n">
-        <v>6809170</v>
+        <v>6809177</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,17 +1308,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127154246</v>
+        <v>127154206</v>
       </c>
       <c r="B8" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1334,26 +1326,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1361,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466177</v>
+        <v>466190</v>
       </c>
       <c r="R8" t="n">
-        <v>6809177</v>
+        <v>6809189</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,7 +1406,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1427,7 +1427,7 @@
         <v>127154796</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 31161-2025 artfynd.xlsx
+++ b/artfynd/A 31161-2025 artfynd.xlsx
@@ -1103,47 +1103,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127154682</v>
+        <v>127154246</v>
       </c>
       <c r="B6" t="n">
-        <v>5176</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1151,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466105</v>
+        <v>466177</v>
       </c>
       <c r="R6" t="n">
-        <v>6809170</v>
+        <v>6809177</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127154246</v>
+        <v>127154206</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,26 +1215,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1252,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466177</v>
+        <v>466190</v>
       </c>
       <c r="R7" t="n">
-        <v>6809177</v>
+        <v>6809189</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,7 +1295,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1315,32 +1313,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127154206</v>
+        <v>127154682</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>5176</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1348,11 +1346,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1362,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466190</v>
+        <v>466105</v>
       </c>
       <c r="R8" t="n">
-        <v>6809189</v>
+        <v>6809170</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,6 +1405,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31161-2025 artfynd.xlsx
+++ b/artfynd/A 31161-2025 artfynd.xlsx
@@ -1204,32 +1204,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127154206</v>
+        <v>127154682</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>5176</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1237,11 +1237,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1251,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466190</v>
+        <v>466105</v>
       </c>
       <c r="R7" t="n">
-        <v>6809189</v>
+        <v>6809170</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,6 +1296,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1313,32 +1315,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127154682</v>
+        <v>127154206</v>
       </c>
       <c r="B8" t="n">
-        <v>5176</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1346,12 +1348,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1361,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466105</v>
+        <v>466190</v>
       </c>
       <c r="R8" t="n">
-        <v>6809170</v>
+        <v>6809189</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,7 +1406,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31161-2025 artfynd.xlsx
+++ b/artfynd/A 31161-2025 artfynd.xlsx
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127154246</v>
+        <v>127154206</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,26 +1114,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1141,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466177</v>
+        <v>466190</v>
       </c>
       <c r="R6" t="n">
-        <v>6809177</v>
+        <v>6809189</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1194,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1204,47 +1212,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127154682</v>
+        <v>127154246</v>
       </c>
       <c r="B7" t="n">
-        <v>5176</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1252,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466105</v>
+        <v>466177</v>
       </c>
       <c r="R7" t="n">
-        <v>6809170</v>
+        <v>6809177</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,32 +1313,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127154206</v>
+        <v>127154682</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>5176</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1348,11 +1346,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1362,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466190</v>
+        <v>466105</v>
       </c>
       <c r="R8" t="n">
-        <v>6809189</v>
+        <v>6809170</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,6 +1405,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31161-2025 artfynd.xlsx
+++ b/artfynd/A 31161-2025 artfynd.xlsx
@@ -1212,37 +1212,47 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127154246</v>
+        <v>127154682</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>5176</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1250,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466177</v>
+        <v>466105</v>
       </c>
       <c r="R7" t="n">
-        <v>6809177</v>
+        <v>6809170</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,47 +1323,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127154682</v>
+        <v>127154246</v>
       </c>
       <c r="B8" t="n">
-        <v>5176</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466105</v>
+        <v>466177</v>
       </c>
       <c r="R8" t="n">
-        <v>6809170</v>
+        <v>6809177</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 31161-2025 artfynd.xlsx
+++ b/artfynd/A 31161-2025 artfynd.xlsx
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127154206</v>
+        <v>127154246</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,35 +1114,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1150,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466190</v>
+        <v>466177</v>
       </c>
       <c r="R6" t="n">
-        <v>6809189</v>
+        <v>6809177</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,6 +1185,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1212,32 +1204,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127154682</v>
+        <v>127154206</v>
       </c>
       <c r="B7" t="n">
-        <v>5176</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1245,12 +1237,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1260,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466105</v>
+        <v>466190</v>
       </c>
       <c r="R7" t="n">
-        <v>6809170</v>
+        <v>6809189</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1295,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1323,37 +1313,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127154246</v>
+        <v>127154682</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>5176</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466177</v>
+        <v>466105</v>
       </c>
       <c r="R8" t="n">
-        <v>6809177</v>
+        <v>6809170</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 31161-2025 artfynd.xlsx
+++ b/artfynd/A 31161-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127154201</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127154687</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127154208</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>127154269</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>127154246</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>127154206</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>127154682</v>
       </c>
       <c r="B8" t="n">
-        <v>5176</v>
+        <v>5177</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>127154796</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31161-2025 artfynd.xlsx
+++ b/artfynd/A 31161-2025 artfynd.xlsx
@@ -1204,32 +1204,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127154206</v>
+        <v>127154682</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>5177</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1237,11 +1237,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1251,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466190</v>
+        <v>466105</v>
       </c>
       <c r="R7" t="n">
-        <v>6809189</v>
+        <v>6809170</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,6 +1296,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1313,32 +1315,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127154682</v>
+        <v>127154206</v>
       </c>
       <c r="B8" t="n">
-        <v>5177</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1346,12 +1348,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1361,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466105</v>
+        <v>466190</v>
       </c>
       <c r="R8" t="n">
-        <v>6809170</v>
+        <v>6809189</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,7 +1406,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31161-2025 artfynd.xlsx
+++ b/artfynd/A 31161-2025 artfynd.xlsx
@@ -1204,32 +1204,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127154682</v>
+        <v>127154206</v>
       </c>
       <c r="B7" t="n">
-        <v>5177</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1237,12 +1237,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1252,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466105</v>
+        <v>466190</v>
       </c>
       <c r="R7" t="n">
-        <v>6809170</v>
+        <v>6809189</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,7 +1295,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1315,32 +1313,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127154206</v>
+        <v>127154682</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>5177</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1348,11 +1346,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1362,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466190</v>
+        <v>466105</v>
       </c>
       <c r="R8" t="n">
-        <v>6809189</v>
+        <v>6809170</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,6 +1405,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31161-2025 artfynd.xlsx
+++ b/artfynd/A 31161-2025 artfynd.xlsx
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127154246</v>
+        <v>127154206</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,26 +1114,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1141,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466177</v>
+        <v>466190</v>
       </c>
       <c r="R6" t="n">
-        <v>6809177</v>
+        <v>6809189</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1194,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1204,32 +1212,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127154206</v>
+        <v>127154682</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>5177</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1237,11 +1245,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1251,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466190</v>
+        <v>466105</v>
       </c>
       <c r="R7" t="n">
-        <v>6809189</v>
+        <v>6809170</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,6 +1304,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1313,47 +1323,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127154682</v>
+        <v>127154246</v>
       </c>
       <c r="B8" t="n">
-        <v>5177</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466105</v>
+        <v>466177</v>
       </c>
       <c r="R8" t="n">
-        <v>6809170</v>
+        <v>6809177</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 31161-2025 artfynd.xlsx
+++ b/artfynd/A 31161-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127154201</v>
       </c>
       <c r="B2" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127154687</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127154208</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>127154269</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127154206</v>
+        <v>127154682</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>5177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1136,11 +1136,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1150,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466190</v>
+        <v>466105</v>
       </c>
       <c r="R6" t="n">
-        <v>6809189</v>
+        <v>6809170</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,6 +1195,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1212,47 +1214,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127154682</v>
+        <v>127154246</v>
       </c>
       <c r="B7" t="n">
-        <v>5177</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1260,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466105</v>
+        <v>466177</v>
       </c>
       <c r="R7" t="n">
-        <v>6809170</v>
+        <v>6809177</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127154246</v>
+        <v>127154206</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1334,26 +1326,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1361,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466177</v>
+        <v>466190</v>
       </c>
       <c r="R8" t="n">
-        <v>6809177</v>
+        <v>6809189</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,7 +1406,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1427,7 +1427,7 @@
         <v>127154796</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31161-2025 artfynd.xlsx
+++ b/artfynd/A 31161-2025 artfynd.xlsx
@@ -1103,47 +1103,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127154682</v>
+        <v>127154246</v>
       </c>
       <c r="B6" t="n">
-        <v>5177</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1151,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466105</v>
+        <v>466177</v>
       </c>
       <c r="R6" t="n">
-        <v>6809170</v>
+        <v>6809177</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127154246</v>
+        <v>127154206</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,26 +1215,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1252,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466177</v>
+        <v>466190</v>
       </c>
       <c r="R7" t="n">
-        <v>6809177</v>
+        <v>6809189</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,7 +1295,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1315,32 +1313,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127154206</v>
+        <v>127154682</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>5177</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1348,11 +1346,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1362,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466190</v>
+        <v>466105</v>
       </c>
       <c r="R8" t="n">
-        <v>6809189</v>
+        <v>6809170</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,6 +1405,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31161-2025 artfynd.xlsx
+++ b/artfynd/A 31161-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127154201</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127154687</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127154208</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>127154269</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,37 +1103,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127154246</v>
+        <v>127154682</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>5177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1141,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466177</v>
+        <v>466105</v>
       </c>
       <c r="R6" t="n">
-        <v>6809177</v>
+        <v>6809170</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127154206</v>
+        <v>127154246</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>79023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,35 +1225,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1251,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466190</v>
+        <v>466177</v>
       </c>
       <c r="R7" t="n">
-        <v>6809189</v>
+        <v>6809177</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,6 +1296,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1313,32 +1315,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127154682</v>
+        <v>127154206</v>
       </c>
       <c r="B8" t="n">
-        <v>5177</v>
+        <v>57666</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1346,12 +1348,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1361,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466105</v>
+        <v>466190</v>
       </c>
       <c r="R8" t="n">
-        <v>6809170</v>
+        <v>6809189</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,7 +1406,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1427,7 +1427,7 @@
         <v>127154796</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31161-2025 artfynd.xlsx
+++ b/artfynd/A 31161-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127154201</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127154687</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127154208</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>127154269</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,47 +1103,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127154682</v>
+        <v>127154246</v>
       </c>
       <c r="B6" t="n">
-        <v>5177</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1151,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466105</v>
+        <v>466177</v>
       </c>
       <c r="R6" t="n">
-        <v>6809170</v>
+        <v>6809177</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127154246</v>
+        <v>127154206</v>
       </c>
       <c r="B7" t="n">
-        <v>79023</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,26 +1215,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1252,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466177</v>
+        <v>466190</v>
       </c>
       <c r="R7" t="n">
-        <v>6809177</v>
+        <v>6809189</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,7 +1295,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1315,32 +1313,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127154206</v>
+        <v>127154682</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>5177</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1348,11 +1346,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1362,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466190</v>
+        <v>466105</v>
       </c>
       <c r="R8" t="n">
-        <v>6809189</v>
+        <v>6809170</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,6 +1405,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1427,7 +1427,7 @@
         <v>127154796</v>
       </c>
       <c r="B9" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 31161-2025 artfynd.xlsx
+++ b/artfynd/A 31161-2025 artfynd.xlsx
@@ -1204,32 +1204,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127154206</v>
+        <v>127154682</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>5177</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1237,11 +1237,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1251,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466190</v>
+        <v>466105</v>
       </c>
       <c r="R7" t="n">
-        <v>6809189</v>
+        <v>6809170</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,6 +1296,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1313,32 +1315,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127154682</v>
+        <v>127154206</v>
       </c>
       <c r="B8" t="n">
-        <v>5177</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1346,12 +1348,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1361,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466105</v>
+        <v>466190</v>
       </c>
       <c r="R8" t="n">
-        <v>6809170</v>
+        <v>6809189</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,7 +1406,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31161-2025 artfynd.xlsx
+++ b/artfynd/A 31161-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127154201</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -787,7 +787,7 @@
         <v>127154687</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -896,7 +896,7 @@
         <v>127154208</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -997,7 +997,7 @@
         <v>127154269</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,17 +1096,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127154246</v>
+        <v>127154206</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,26 +1114,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1141,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466177</v>
+        <v>466190</v>
       </c>
       <c r="R6" t="n">
-        <v>6809177</v>
+        <v>6809189</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1194,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1197,7 +1205,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1207,7 +1215,7 @@
         <v>127154682</v>
       </c>
       <c r="B7" t="n">
-        <v>5177</v>
+        <v>5176</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,17 +1316,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127154206</v>
+        <v>127154246</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1326,35 +1334,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1362,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466190</v>
+        <v>466177</v>
       </c>
       <c r="R8" t="n">
-        <v>6809189</v>
+        <v>6809177</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,6 +1405,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1427,7 +1427,7 @@
         <v>127154796</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 31161-2025 artfynd.xlsx
+++ b/artfynd/A 31161-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,46 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127154201</v>
+        <v>127153668</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466193</v>
+        <v>466206</v>
       </c>
       <c r="R2" t="n">
-        <v>6809194</v>
+        <v>6809201</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -784,46 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127154687</v>
+        <v>127153712</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466105</v>
+        <v>466164</v>
       </c>
       <c r="R3" t="n">
-        <v>6809170</v>
+        <v>6809202</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,38 +852,44 @@
           <t>2025-08-04</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Måttligt på gran</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127154208</v>
+        <v>127154119</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -931,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466190</v>
+        <v>466247</v>
       </c>
       <c r="R4" t="n">
-        <v>6809189</v>
+        <v>6809203</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,46 +983,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127154269</v>
+        <v>127154208</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1041,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466160</v>
+        <v>466190</v>
       </c>
       <c r="R5" t="n">
-        <v>6809168</v>
+        <v>6809189</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,6 +1065,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1103,14 +1084,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127154246</v>
+        <v>127154219</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1141,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466177</v>
+        <v>466218</v>
       </c>
       <c r="R6" t="n">
-        <v>6809177</v>
+        <v>6809163</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1166,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1204,47 +1184,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127154682</v>
+        <v>127154246</v>
       </c>
       <c r="B7" t="n">
-        <v>5177</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1252,10 +1222,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>466105</v>
+        <v>466177</v>
       </c>
       <c r="R7" t="n">
-        <v>6809170</v>
+        <v>6809177</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,46 +1285,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127154206</v>
+        <v>127154796</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1362,10 +1323,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>466190</v>
+        <v>466096</v>
       </c>
       <c r="R8" t="n">
-        <v>6809189</v>
+        <v>6809177</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,6 +1367,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1424,14 +1386,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127154796</v>
+        <v>127155066</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1462,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>466096</v>
+        <v>466046</v>
       </c>
       <c r="R9" t="n">
-        <v>6809177</v>
+        <v>6809186</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,6 +1484,3843 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127155475</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>466076</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6809225</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127155499</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>466085</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6809224</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127154103</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>466254</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6809208</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127154111</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>466259</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6809208</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127154201</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>466193</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6809194</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127154206</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>466190</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6809189</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127154269</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>466160</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6809168</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127154595</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>466128</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6809202</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127154600</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>466144</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6809220</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127154687</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>466105</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6809170</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127155126</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>466040</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6809191</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127155460</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>466067</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6809228</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127155482</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>466081</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6809216</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127154630</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>466148</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6809222</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127154682</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>466105</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6809170</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127155506</v>
+      </c>
+      <c r="B25" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>466085</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6809224</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127154181</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>466206</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6809201</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127154223</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>466218</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6809163</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127154233</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>466218</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6809163</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127154066</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>466274</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6809202</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127154092</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>466255</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6809216</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127154126</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>466247</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6809203</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127154614</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>466148</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6809222</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>sälg intill bäck</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127153742</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>466410</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6809205</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127153768</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>466392</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6809204</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>rikl</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127153795</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>466388</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6809208</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127153801</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>466383</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6809213</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127153848</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>466359</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6809211</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127153858</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>466333</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6809211</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127153920</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>466298</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6809205</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127153844</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80460</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>466359</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6809211</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127153709</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>466410</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6809209</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127153754</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>466399</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6809202</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127153899</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>466299</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6809206</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127153911</v>
+      </c>
+      <c r="B44" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>466299</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6809206</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127153894</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>N Itavsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>466299</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6809206</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31161-2025 artfynd.xlsx
+++ b/artfynd/A 31161-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153668</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153712</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153742</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153768</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153795</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153801</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,6 +1424,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153848</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153858</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1591,6 +1636,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153920</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154119</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1793,6 +1848,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154208</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1893,6 +1953,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154219</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1994,6 +2059,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154246</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2095,6 +2165,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154796</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2196,6 +2271,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155066</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2297,6 +2377,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155475</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2398,6 +2483,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153844</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2507,6 +2597,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155499</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2621,6 +2716,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153709</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2730,6 +2830,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153754</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2835,6 +2940,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153899</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2944,6 +3054,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154103</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3053,6 +3168,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154111</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3162,6 +3282,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154201</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3271,6 +3396,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154206</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3380,6 +3510,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154269</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3489,6 +3624,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154595</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3598,6 +3738,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154600</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3707,6 +3852,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154687</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3816,6 +3966,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155126</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3925,6 +4080,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155460</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4034,6 +4194,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155482</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4143,6 +4308,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154630</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4254,6 +4424,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154682</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4361,6 +4536,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127155506</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4463,6 +4643,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154181</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4564,6 +4749,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154223</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4666,6 +4856,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153911</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4767,6 +4962,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154233</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4877,6 +5077,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127153894</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4987,6 +5192,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154066</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5097,6 +5307,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154092</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5207,6 +5422,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154126</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5321,8 +5541,59 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127154614</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>